--- a/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E734DD-25DE-4117-B5F4-B64262A987B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E89A85-0A25-40AA-A891-3868F722826F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>##var</t>
   </si>
@@ -75,6 +75,9 @@
     <t>desc</t>
   </si>
   <si>
+    <t>mmc_logic</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -84,62 +87,48 @@
     <t>string</t>
   </si>
   <si>
+    <t>MmcLogic?</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
-    <t>GameplayCueLog</t>
-  </si>
-  <si>
-    <t>testMessageA</t>
-  </si>
-  <si>
-    <t>CueLoging</t>
-  </si>
-  <si>
-    <t>testValue2</t>
-  </si>
-  <si>
     <t>名字</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>mmc_logic</t>
-    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>作用描述</t>
   </si>
   <si>
     <t>mmc修改器计算逻辑：支持多态，添加新CueLogic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>模值x1.5</t>
-    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述:模值x1.5</t>
+  </si>
+  <si>
+    <t>MMCScalableFloat</t>
   </si>
   <si>
     <t>模值x3</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>作用描述</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>描述:模值x1.5</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>描述:模值x3</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>MmcLogic?</t>
-    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试3</t>
+  </si>
+  <si>
+    <t>test message3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,21 +142,6 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -273,47 +247,49 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -594,13 +570,13 @@
   <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.21875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1" style="5"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1" style="5"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1" style="5"/>
+    <col min="6" max="6" width="15" customWidth="1" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -613,214 +589,231 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="7"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="9"/>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="10"/>
-    </row>
-    <row r="3" spans="1:18" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="12"/>
+    </row>
+    <row r="3" ht="14.4">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="13"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="15"/>
+    </row>
+    <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="F4" s="6">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1002</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="6">
+        <v>3</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4">
+        <v>1003</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1.5499999523162842</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B6" s="2"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="4"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="E6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8">
       <c r="B8" s="1"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14">
       <c r="B14" s="1"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15">
       <c r="B15" s="1"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16">
       <c r="B16" s="1"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17">
       <c r="B17" s="1"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18">
       <c r="B18" s="1"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19">
       <c r="B19" s="1"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20">
       <c r="B20" s="1"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="B23" s="1"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="4"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25">
+      <c r="B25" s="6"/>
+    </row>
+    <row r="26">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells>
     <mergeCell ref="E1:R1"/>
     <mergeCell ref="E2:R2"/>
     <mergeCell ref="E3:R3"/>
@@ -828,6 +821,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E89A85-0A25-40AA-A891-3868F722826F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810E143D-98E8-4538-9923-4FA380244FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>##var</t>
   </si>
@@ -75,9 +75,6 @@
     <t>desc</t>
   </si>
   <si>
-    <t>mmc_logic</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -121,14 +118,17 @@
   </si>
   <si>
     <t>test message3</t>
+  </si>
+  <si>
+    <t>mmcLogic</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +142,21 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -247,49 +262,48 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -570,13 +584,13 @@
   <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.21875" customWidth="1" style="5"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1" style="5"/>
-    <col min="5" max="5" width="16.77734375" customWidth="1" style="5"/>
-    <col min="6" max="6" width="15" customWidth="1" style="5"/>
+    <col min="3" max="3" width="16.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,231 +603,231 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="8"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="9"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="11"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="12"/>
-    </row>
-    <row r="3" ht="14.4">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="15"/>
-    </row>
-    <row r="4">
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="14"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>2</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1002</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="5">
+        <v>3</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
+        <v>1003</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="6">
-        <v>3</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="4">
-        <v>1003</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="E6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="4">
         <v>1.5</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10">
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11">
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12">
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-    </row>
-    <row r="17">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-    </row>
-    <row r="22">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
     </row>
-    <row r="25">
-      <c r="B25" s="6"/>
-    </row>
-    <row r="26">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="3">
     <mergeCell ref="E1:R1"/>
     <mergeCell ref="E2:R2"/>
     <mergeCell ref="E3:R3"/>
@@ -821,7 +835,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810E143D-98E8-4538-9923-4FA380244FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,12 +24,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>fangmenglu</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{279665AC-3B9C-4E41-8A7C-7EC5099B4FAA}">
+    <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -96,9 +95,6 @@
     <t>作用描述</t>
   </si>
   <si>
-    <t>mmc修改器计算逻辑：支持多态，添加新CueLogic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
-  </si>
-  <si>
     <t>模值x1.5</t>
   </si>
   <si>
@@ -121,13 +117,39 @@
   </si>
   <si>
     <t>mmcLogic</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>mmc修改器计算逻辑：支持多态，添加新</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mmc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Logic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
+    </r>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -291,19 +313,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -580,17 +602,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="16.21875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.5" style="4" customWidth="1"/>
+    <col min="5" max="5" width="16.75" style="4" customWidth="1"/>
     <col min="6" max="6" width="15" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -604,7 +626,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
@@ -620,7 +642,7 @@
       <c r="Q1" s="7"/>
       <c r="R1" s="8"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -650,7 +672,7 @@
       <c r="Q2" s="10"/>
       <c r="R2" s="11"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -663,36 +685,36 @@
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="14"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="E3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="13"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>14</v>
       </c>
       <c r="F4" s="5">
         <v>2</v>
@@ -701,19 +723,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1002</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" s="5">
         <v>3</v>
@@ -722,18 +744,18 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="E6" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" s="4">
         <v>1.5</v>
@@ -742,88 +764,88 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B8" s="1"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B15" s="1"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="1"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="1"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B25" s="5"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" s="1"/>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>##var</t>
   </si>
@@ -74,6 +74,9 @@
     <t>desc</t>
   </si>
   <si>
+    <t>mmcLogic</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -95,35 +98,10 @@
     <t>作用描述</t>
   </si>
   <si>
-    <t>模值x1.5</t>
-  </si>
-  <si>
-    <t>描述:模值x1.5</t>
-  </si>
-  <si>
-    <t>MMCScalableFloat</t>
-  </si>
-  <si>
-    <t>模值x3</t>
-  </si>
-  <si>
-    <t>描述:模值x3</t>
-  </si>
-  <si>
-    <t>测试3</t>
-  </si>
-  <si>
-    <t>test message3</t>
-  </si>
-  <si>
-    <t>mmcLogic</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>mmc修改器计算逻辑：支持多态，添加新</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -133,7 +111,7 @@
       </rPr>
       <t>Mmc</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -143,14 +121,36 @@
       </rPr>
       <t>Logic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
     </r>
-    <phoneticPr fontId="0" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>模值x1</t>
+  </si>
+  <si>
+    <t>描述:模值x1</t>
+  </si>
+  <si>
+    <t>MMCScalableFloat</t>
+  </si>
+  <si>
+    <t>模值x3</t>
+  </si>
+  <si>
+    <t>描述:模值x3</t>
+  </si>
+  <si>
+    <t>测试3</t>
+  </si>
+  <si>
+    <t>test message3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,21 +164,6 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -284,42 +269,43 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -606,13 +592,13 @@
   <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="16.25" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.5" style="4" customWidth="1"/>
-    <col min="5" max="5" width="16.75" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15" style="4" customWidth="1"/>
+    <col min="3" max="3" width="16.25" customWidth="1" style="5"/>
+    <col min="4" max="4" width="14.5" customWidth="1" style="5"/>
+    <col min="5" max="5" width="16.75" customWidth="1" style="5"/>
+    <col min="6" max="6" width="15" customWidth="1" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -625,231 +611,231 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="8"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="9"/>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="11"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="E2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="12"/>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="13"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="14"/>
+    </row>
+    <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="5">
-        <v>2</v>
-      </c>
-      <c r="G4" s="2">
+      <c r="D4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1002</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="F5" s="6">
         <v>3</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="5">
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="B6" s="3">
+    <row r="6">
+      <c r="B6" s="4">
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="4">
+        <v>18</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5">
         <v>1.5</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8">
       <c r="B8" s="1"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14">
       <c r="B14" s="1"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15">
       <c r="B15" s="1"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16">
       <c r="B16" s="1"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17">
       <c r="B17" s="1"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18">
       <c r="B18" s="1"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19">
       <c r="B19" s="1"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20">
       <c r="B20" s="1"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="B23" s="1"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="5"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="25">
+      <c r="B25" s="6"/>
+    </row>
+    <row r="26">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells>
     <mergeCell ref="E1:R1"/>
     <mergeCell ref="E2:R2"/>
     <mergeCell ref="E3:R3"/>
@@ -857,6 +843,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
@@ -1,35 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B241FF0-A396-4BA4-BAA0-B9AD59AED8C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>fangmenglu</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -60,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>##var</t>
   </si>
@@ -86,9 +90,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>MmcLogic?</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -98,10 +99,10 @@
     <t>作用描述</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>mmc修改器计算逻辑：支持多态，添加新</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -111,7 +112,7 @@
       </rPr>
       <t>Mmc</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -121,7 +122,7 @@
       </rPr>
       <t>Logic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>模值x1</t>
@@ -143,14 +144,17 @@
   </si>
   <si>
     <t>test message3</t>
+  </si>
+  <si>
+    <t>MmcLogic</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +168,21 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -269,49 +288,48 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -588,17 +606,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.25" customWidth="1" style="5"/>
-    <col min="4" max="4" width="14.5" customWidth="1" style="5"/>
-    <col min="5" max="5" width="16.75" customWidth="1" style="5"/>
-    <col min="6" max="6" width="15" customWidth="1" style="5"/>
+    <col min="3" max="3" width="16.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -611,24 +629,24 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="9"/>
-    </row>
-    <row r="2">
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="8"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -641,38 +659,38 @@
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="11"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="12"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>12</v>
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
@@ -688,154 +706,154 @@
       <c r="Q3" s="13"/>
       <c r="R3" s="14"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>1</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1002</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="5">
+        <v>3</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
+        <v>1003</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="6">
-        <v>3</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="4">
-        <v>1003</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="E6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="4">
         <v>1.5</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10">
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11">
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12">
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-    </row>
-    <row r="17">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-    </row>
-    <row r="22">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
     </row>
-    <row r="25">
-      <c r="B25" s="6"/>
-    </row>
-    <row r="26">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="3">
     <mergeCell ref="E1:R1"/>
     <mergeCell ref="E2:R2"/>
     <mergeCell ref="E3:R3"/>
@@ -843,7 +861,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B241FF0-A396-4BA4-BAA0-B9AD59AED8C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD40B25-D4C8-440A-8FC7-15DB4459D442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,21 +64,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
   <si>
     <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>mmcLogic</t>
   </si>
   <si>
     <t>##type</t>
@@ -144,6 +135,22 @@
   </si>
   <si>
     <t>test message3</t>
+  </si>
+  <si>
+    <t>MmcLogic</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>MmcLogic</t>
@@ -621,16 +628,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
@@ -648,19 +655,19 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F2" s="10"/>
       <c r="G2" s="10"/>
@@ -678,19 +685,19 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
@@ -712,13 +719,13 @@
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F4" s="5">
         <v>1</v>
@@ -733,13 +740,13 @@
         <v>1002</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F5" s="5">
         <v>3</v>
@@ -753,13 +760,13 @@
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F6" s="4">
         <v>1.5</v>
